--- a/prom.xlsx
+++ b/prom.xlsx
@@ -22091,7 +22091,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>312</v>
+        <v>718</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -22117,7 +22117,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
         <v>143878724</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -11218,7 +11218,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R36" t="n">
         <v>143279711</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
         <v>143279702</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>143279712</v>
@@ -1510,11 +1510,11 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>143279712</v>
@@ -24042,7 +24042,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R81" t="n">
         <v>143878720</v>
@@ -36926,7 +36926,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R128" t="n">
         <v>143878719</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>143279706</v>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>143279706</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
         <v>143279707</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>143279708</v>
@@ -9136,11 +9136,11 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>143279708</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
         <v>143279705</v>
@@ -13570,11 +13570,11 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
         <v>143279703</v>
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
         <v>143279700</v>
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
         <v>143279700</v>
@@ -15970,11 +15970,11 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
         <v>143279709</v>
@@ -28412,7 +28412,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R97" t="n">
         <v>143878725</v>
@@ -33690,7 +33690,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R116" t="n">
         <v>147040394</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -17938,7 +17938,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
         <v>143878719</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5544</v>
+        <v>4200</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -15948,7 +15948,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2520</v>
+        <v>4380</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -15974,7 +15974,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
         <v>143279709</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>143279712</v>
@@ -21020,7 +21020,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R70" t="n">
         <v>143878724</v>
@@ -21843,7 +21843,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R73" t="n">
         <v>143878724</v>
@@ -24042,7 +24042,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R81" t="n">
         <v>143878720</v>
@@ -24323,7 +24323,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R82" t="n">
         <v>143878720</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>143279708</v>
@@ -10924,11 +10924,11 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>143279711</v>
@@ -15970,11 +15970,11 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>143279709</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -15672,7 +15672,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
         <v>143279709</v>
@@ -41178,11 +41178,11 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R144" t="n">
         <v>143279708</v>
@@ -41708,11 +41708,11 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" t="n">
         <v>143279708</v>
@@ -41989,11 +41989,11 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R147" t="n">
         <v>143279708</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>143279706</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3120</v>
+        <v>3528</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7200</v>
+        <v>8160</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -2916,11 +2916,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>143279702</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>143279712</v>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
         <v>143279708</v>
@@ -10050,11 +10050,11 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>143279711</v>
@@ -15970,11 +15970,11 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
         <v>143279709</v>
@@ -27027,11 +27027,11 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
         <v>143279712</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -37425,7 +37425,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1080</v>
+        <v>1200</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
         <v>143279706</v>
@@ -37451,7 +37451,7 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R130" t="n">
         <v>143878726</v>
@@ -37989,11 +37989,11 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>143878726</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -17396,7 +17396,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
         <v>143279709</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -29252,7 +29252,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R100" t="n">
         <v>143878725</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>16920</v>
+        <v>15120</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6660</v>
+        <v>8694</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -38768,11 +38768,11 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>143878726</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>143279702</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
         <v>143279712</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R94" t="n">
         <v>143878725</v>
@@ -39859,11 +39859,11 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R139" t="n">
         <v>143279704</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -15970,11 +15970,11 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>143279709</v>
@@ -16844,7 +16844,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
         <v>143279704</v>
@@ -17396,7 +17396,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
         <v>143279709</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -11794,11 +11794,11 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>143279711</v>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R94" t="n">
         <v>143878725</v>
@@ -28412,7 +28412,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="R97" t="n">
         <v>143878725</v>
@@ -31741,11 +31741,11 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R109" t="n">
         <v>147040391</v>
@@ -32037,7 +32037,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
         <v>147040391</v>
@@ -32293,11 +32293,11 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
         <v>147040391</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>143279702</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -2916,11 +2916,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>143279702</v>
@@ -11504,11 +11504,11 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>143279711</v>

--- a/prom.xlsx
+++ b/prom.xlsx
@@ -37170,7 +37170,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>276</v>
+        <v>378</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
